--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>94783</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,12 +765,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96327</v>
+        <v>96330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96330</v>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96338</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96349</v>
+        <v>96350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96350</v>
+        <v>96351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96351</v>
+        <v>96353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96353</v>
+        <v>96354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
+        <v>96357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43163-2025 artfynd.xlsx
+++ b/artfynd/A 43163-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122743640</v>
       </c>
       <c r="B2" t="n">
-        <v>96357</v>
+        <v>96425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,208 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122743641</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gropen NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>565459</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6881609</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122743642</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gropen NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565433</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6881771</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
